--- a/01_設計/デザイン関係資料/spectra_chat_画面案.xlsx
+++ b/01_設計/デザイン関係資料/spectra_chat_画面案.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keita\Desktop\programing\nextjs\OpenDataChallenge\01_設計\デザイン関係資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55C6E431-2497-4E53-9906-2CFA6479F8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5477603-3889-4B2D-BC02-2C691C2AE804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="チャット操作画面" sheetId="1" r:id="rId1"/>
+    <sheet name="レイヤー操作画面" sheetId="3" r:id="rId2"/>
+    <sheet name="コンポーネント" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -81,9 +82,11 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCAB2FB"/>
+      <color rgb="FFB28DD9"/>
+      <color rgb="FF808080"/>
+      <color rgb="FFC3FF4B"/>
       <color rgb="FF333333"/>
-      <color rgb="FFC3FF4B"/>
-      <color rgb="FF808080"/>
     </mruColors>
   </colors>
   <extLst>
@@ -696,220 +699,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>9668</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>221532</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>211833</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>105253</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="31" name="グループ化 30">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C5090A5-D659-77C4-B931-DBADABEE0F15}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="1373247" y="7440479"/>
-          <a:ext cx="7701849" cy="1808774"/>
-          <a:chOff x="3720021" y="4894643"/>
-          <a:chExt cx="7724473" cy="1837567"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="28" name="四角形: 上の 2 つの角を丸める 27">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21030408-3A4D-8E33-55B3-7A49BC9C8D9F}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3720021" y="4894643"/>
-            <a:ext cx="7722832" cy="540599"/>
-          </a:xfrm>
-          <a:prstGeom prst="round2SameRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="50800" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:schemeClr val="tx1"/>
-            </a:outerShdw>
-          </a:effectLst>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="29" name="正方形/長方形 28">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EB1EBBD-13C5-44DB-86CE-BF38CF34CEC3}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3720022" y="5439841"/>
-            <a:ext cx="7724472" cy="1292369"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="50800" dist="38100" dir="15360000" algn="t" rotWithShape="0">
-              <a:prstClr val="black">
-                <a:alpha val="40000"/>
-              </a:prstClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="30" name="テキスト ボックス 29">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC00EE4F-6CE1-C2A4-89AC-FEDF486632B7}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr txBox="1"/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3834424" y="4957884"/>
-            <a:ext cx="2369038" cy="378559"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="9525" cmpd="sng">
-            <a:noFill/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:scrgbClr r="0" g="0" b="0"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="1">
-                <a:solidFill>
-                  <a:schemeClr val="bg1"/>
-                </a:solidFill>
-                <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
-                <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
-              </a:rPr>
-              <a:t>チャットで質問</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>431799</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
+      <xdr:rowOff>80879</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>680356</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:rowOff>182479</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -924,7 +723,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9976852" y="291432"/>
+          <a:off x="9976852" y="321511"/>
           <a:ext cx="3657504" cy="6358021"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1569,18 +1368,3845 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>4572</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>120556</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58287916-F674-4B19-BE95-47FF38188F32}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="20016791" cy="11540837"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>676274</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>53264</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>666749</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>135524</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="3" name="グループ化 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DF4A750-7758-443C-912B-A0879FBF3363}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="1366351" y="296249"/>
+          <a:ext cx="12411852" cy="6399862"/>
+          <a:chOff x="1360883" y="255445"/>
+          <a:chExt cx="12313444" cy="6273510"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="4" name="図 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EF3775A-EF8B-8BB8-2AAD-B1551A5BA5ED}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="1360883" y="260821"/>
+            <a:ext cx="12313444" cy="6263804"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:extLst>
+            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a14:hiddenFill>
+            </a:ext>
+          </a:extLst>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="5" name="正方形/長方形 4">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76F1E40C-D8C7-4C33-C987-78E541C82EC9}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1360884" y="255445"/>
+            <a:ext cx="692944" cy="6273510"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="C3FF4B"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="50800" dist="50800" sx="99000" sy="99000" algn="ctr" rotWithShape="0">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+              </a:schemeClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>668789</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>203027</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>13945</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>108770</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="テキスト ボックス 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94A6DCB6-B546-4A7B-B08A-5A49D102CE4A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="450408" y="1821583"/>
+          <a:ext cx="2525118" cy="716756"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" b="1">
+              <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>SPECTRA</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" b="1" baseline="0">
+              <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" b="1" baseline="0">
+              <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>CHAT</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" b="1">
+            <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>119458</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>188514</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>576658</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>169464</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="グラフィックス 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27ED7DA2-BCE0-48B1-B73F-779440BE865A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="1491058" y="426639"/>
+          <a:ext cx="457200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>173991</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>107605</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>478791</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>174706</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="グラフィックス 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F436184-652A-4814-9641-3D66BB1EF909}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId5"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1545591" y="3917605"/>
+          <a:ext cx="304800" cy="305226"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>116227</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>199451</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>573427</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>200532</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="直線コネクタ 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54A2A3D5-A8B3-4A1E-A9EB-CFB38AA62D71}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1487827" y="3533201"/>
+          <a:ext cx="457200" cy="1081"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>185898</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>40184</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>490698</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>98805</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="グラフィックス 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED95F101-0AE4-40DE-8594-9ED01CC3C4EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId7"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1557498" y="4564559"/>
+          <a:ext cx="304800" cy="296746"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>182702</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>137599</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>487502</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>204274</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="グラフィックス 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A707C623-0547-4C9B-B739-1F7BE448A9E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId9"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1554302" y="5852599"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>170457</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>222715</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>475257</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>49600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="グラフィックス 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42D6D198-AE67-493B-804C-EFE78DCE676B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId11"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1542057" y="5223340"/>
+          <a:ext cx="304800" cy="303135"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>431799</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>80879</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>680356</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>182479</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="正方形/長方形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C08556B9-1C0F-4C80-A47D-FE327F4F8844}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10092870" y="323864"/>
+          <a:ext cx="3698940" cy="6419202"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="50800" dir="10320000" algn="ctr" rotWithShape="0">
+            <a:schemeClr val="bg2">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>427651</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>51955</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>212480</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>214021</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="正方形/長方形 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B86BC7D0-1794-4B96-B5E4-836A59FF985E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10004606" y="290080"/>
+          <a:ext cx="1837033" cy="400191"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="333333"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>210715</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>45487</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>680962</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>213646</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="正方形/長方形 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{869A9622-1257-4A2C-9F50-106CAC07A5FB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11869315" y="283612"/>
+          <a:ext cx="1841847" cy="406284"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="C3FF4B"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>221925</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>49088</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>680961</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>115693</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="正方形/長方形 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F998DA5-FEFB-4E70-91F0-9BB25C828264}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11885054" y="768459"/>
+          <a:ext cx="1831169" cy="66605"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="C3FF4B"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>340179</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>48597</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>340180</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>155511</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="テキスト ボックス 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E973722D-683D-4166-8803-AB403EE00C2E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10627179" y="286722"/>
+          <a:ext cx="685801" cy="345039"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>CHAT</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>23327</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>40924</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>147838</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="テキスト ボックス 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A2AA7E0-00CD-4C94-96D1-3EDBB6292EA9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12367727" y="279049"/>
+          <a:ext cx="852973" cy="345039"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>LAYERS</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>427653</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>29158</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>680357</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>136071</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="40" name="グループ化 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3303CA2D-CC61-A2E1-EF4C-7B3B119EFB92}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="10088724" y="1001097"/>
+          <a:ext cx="3703087" cy="835867"/>
+          <a:chOff x="10088724" y="1001097"/>
+          <a:chExt cx="3703087" cy="835867"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="37" name="正方形/長方形 36">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F691508C-837C-FAA3-84DB-5AD1739E4FD4}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10088724" y="1001097"/>
+            <a:ext cx="3703087" cy="835867"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="23" name="テキスト ボックス 22">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42E19AB4-BD1B-4B31-170C-1F8B7EEF4081}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10601805" y="1255027"/>
+            <a:ext cx="1670916" cy="413433"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+                <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>鉄道　駅</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="25" name="グラフィックス 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1ED27A9-98BB-AC15-E445-08E10B850058}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12">
+            <a:extLst>
+              <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+                <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId13"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10272675" y="1335239"/>
+            <a:ext cx="313088" cy="307154"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="28" name="直線コネクタ 27">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD84DEF0-F15F-4AD0-AD7E-E6D627CFBE90}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10183107" y="1752774"/>
+            <a:ext cx="3539952" cy="18303"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:solidFill>
+              <a:srgbClr val="808080"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="31" name="四角形: 角を丸くする 30">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4257B93-1712-552F-E90D-17093CE8A7DD}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10282703" y="1082228"/>
+            <a:ext cx="659998" cy="173802"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="32" name="四角形: 角を丸くする 31">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26822946-7A4E-4C5D-BEAA-9891A856576C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11024918" y="1084234"/>
+            <a:ext cx="659996" cy="173802"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="33" name="四角形: 角を丸くする 32">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B271E36-6DB7-4BA0-9544-824219A94A11}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11757585" y="1084020"/>
+            <a:ext cx="656969" cy="173802"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="36" name="図 35">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE09DCD8-C71F-8D5C-7E8B-19DB39C4687D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="13412755" y="1331556"/>
+            <a:ext cx="304800" cy="304800"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>424543</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>132961</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>677247</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>239874</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="42" name="グループ化 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2297D52-8186-43C2-9E06-08CBAC6D476D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="10085614" y="1833854"/>
+          <a:ext cx="3703087" cy="835867"/>
+          <a:chOff x="10088724" y="1001097"/>
+          <a:chExt cx="3703087" cy="835867"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="43" name="正方形/長方形 42">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1B68FBA-15CD-D68D-4912-EF87AA77C4D1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10088724" y="1001097"/>
+            <a:ext cx="3703087" cy="835867"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="44" name="テキスト ボックス 43">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5D86ACF-EAC9-6BA1-8F7C-21406C54F105}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10601805" y="1255027"/>
+            <a:ext cx="1670916" cy="413433"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+                <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>鉄道　駅</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="45" name="グラフィックス 44">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53652B79-48CF-A4B8-AE1A-B6D987889115}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12">
+            <a:extLst>
+              <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+                <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId13"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10272675" y="1335239"/>
+            <a:ext cx="313088" cy="307154"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="46" name="直線コネクタ 45">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{611BB66B-10A6-75CA-DE20-EAB9504C6302}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10183107" y="1752774"/>
+            <a:ext cx="3539952" cy="18303"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:solidFill>
+              <a:srgbClr val="808080"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="47" name="四角形: 角を丸くする 46">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B929D3D2-1F6F-18F2-A6F1-3DB29865D861}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10282703" y="1082228"/>
+            <a:ext cx="659998" cy="173802"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="48" name="四角形: 角を丸くする 47">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B94E8FB7-80B6-023E-A52E-BE2E36AD4D6E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11024918" y="1084234"/>
+            <a:ext cx="659996" cy="173802"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="49" name="四角形: 角を丸くする 48">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AF9CFEE-710A-5128-58C2-094C0AC292BA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11757585" y="1084020"/>
+            <a:ext cx="656969" cy="173802"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="50" name="図 49">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DD6E014-A6F7-790B-DBB8-D315B42C6B46}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="13412755" y="1331556"/>
+            <a:ext cx="304800" cy="304800"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>431152</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>3499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>683856</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>110412</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="51" name="グループ化 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1695A10D-8B20-4159-BA4F-0DA4BBDF3D70}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="10092223" y="2676331"/>
+          <a:ext cx="3703087" cy="835867"/>
+          <a:chOff x="10088724" y="1001097"/>
+          <a:chExt cx="3703087" cy="835867"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="52" name="正方形/長方形 51">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4996BA9C-EB81-C2D0-3F4F-83B0765273D6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10088724" y="1001097"/>
+            <a:ext cx="3703087" cy="835867"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="53" name="テキスト ボックス 52">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83D50CC5-8E29-AA49-6AE6-274A40512CCD}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10601805" y="1255027"/>
+            <a:ext cx="1670916" cy="413433"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+                <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>鉄道　駅</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="54" name="グラフィックス 53">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{633B1B74-C130-C185-D5FD-998224DD417B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12">
+            <a:extLst>
+              <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+                <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId13"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10272675" y="1335239"/>
+            <a:ext cx="313088" cy="307154"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="55" name="直線コネクタ 54">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DA5832E-8A67-6CC5-BB8A-FC9245E1D43D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10183107" y="1752774"/>
+            <a:ext cx="3539952" cy="18303"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:solidFill>
+              <a:srgbClr val="808080"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="56" name="四角形: 角を丸くする 55">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E9EBD6A-5908-D71C-E601-3DF4EA4697DC}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10282703" y="1082228"/>
+            <a:ext cx="659998" cy="173802"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="57" name="四角形: 角を丸くする 56">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1B2E0E7-3B79-F787-7490-C90FDBF4128B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11024918" y="1084234"/>
+            <a:ext cx="659996" cy="173802"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="58" name="四角形: 角を丸くする 57">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE1F1692-6A60-2C5B-02B4-432BE92472E1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11757585" y="1084020"/>
+            <a:ext cx="656969" cy="173802"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="59" name="図 58">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09B89A2B-9CDC-1D5D-2195-752D7B2EFFC3}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="13412755" y="1331556"/>
+            <a:ext cx="304800" cy="304800"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>428042</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>107302</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>680746</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>214215</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="60" name="グループ化 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E831C52-6943-4355-A172-FA89CF6D15D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="10089113" y="3509088"/>
+          <a:ext cx="3703087" cy="835867"/>
+          <a:chOff x="10088724" y="1001097"/>
+          <a:chExt cx="3703087" cy="835867"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="61" name="正方形/長方形 60">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F2EA66B-26FC-9473-E278-EA6FE9DE97F1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10088724" y="1001097"/>
+            <a:ext cx="3703087" cy="835867"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="62" name="テキスト ボックス 61">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{017638BD-0F85-2653-CA46-7724A0C9E5E7}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10601805" y="1255027"/>
+            <a:ext cx="1670916" cy="413433"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+                <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>鉄道　駅</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="63" name="グラフィックス 62">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE0F1024-5BF7-ACD2-3526-53EFABBACA62}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12">
+            <a:extLst>
+              <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+                <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId13"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10272675" y="1335239"/>
+            <a:ext cx="313088" cy="307154"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="64" name="直線コネクタ 63">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E501A1F-2A9E-53FC-D8D6-5206B490A577}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10183107" y="1752774"/>
+            <a:ext cx="3539952" cy="18303"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:solidFill>
+              <a:srgbClr val="808080"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="65" name="四角形: 角を丸くする 64">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9A3F6A8-9398-D098-0BE4-2FDB7E7BCA29}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10282703" y="1082228"/>
+            <a:ext cx="659998" cy="173802"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="66" name="四角形: 角を丸くする 65">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2189FA6-B62D-A2A3-3EE4-87F4180132BA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11024918" y="1084234"/>
+            <a:ext cx="659996" cy="173802"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="67" name="四角形: 角を丸くする 66">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDBE1E11-C047-2E2E-03A6-22A4B51E9C5F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11757585" y="1084020"/>
+            <a:ext cx="656969" cy="173802"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="68" name="図 67">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20CDBBF0-2D90-3CBE-37C0-46F1CD1AA646}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="13412755" y="1331556"/>
+            <a:ext cx="304800" cy="304800"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>424931</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>211105</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>677635</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>75033</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="69" name="グループ化 68">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEE92840-0BF6-4042-907E-76E25AF42FDF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="10086002" y="4341845"/>
+          <a:ext cx="3703087" cy="835867"/>
+          <a:chOff x="10088724" y="1001097"/>
+          <a:chExt cx="3703087" cy="835867"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="70" name="正方形/長方形 69">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D38369D3-140E-9D9E-E461-01E0D6CBB738}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10088724" y="1001097"/>
+            <a:ext cx="3703087" cy="835867"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="71" name="テキスト ボックス 70">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77429620-293A-97C6-A84F-E93EE81D88AE}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10601805" y="1255027"/>
+            <a:ext cx="1670916" cy="413433"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+                <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>鉄道　駅</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="72" name="グラフィックス 71">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E31FEAA2-564E-7BFB-779F-AD6D16D25228}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12">
+            <a:extLst>
+              <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+                <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId13"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10272675" y="1335239"/>
+            <a:ext cx="313088" cy="307154"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="73" name="直線コネクタ 72">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE6196C3-E39E-A337-22A0-C57EAB819758}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10183107" y="1752774"/>
+            <a:ext cx="3539952" cy="18303"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:solidFill>
+              <a:srgbClr val="808080"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="74" name="四角形: 角を丸くする 73">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{109A38CB-CB19-39A8-A8BA-F9F04498A8FD}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10282703" y="1082228"/>
+            <a:ext cx="659998" cy="173802"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="75" name="四角形: 角を丸くする 74">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{711C309A-190C-570D-9AFC-9E945FD6DB15}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11024918" y="1084234"/>
+            <a:ext cx="659996" cy="173802"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="76" name="四角形: 角を丸くする 75">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F6BB901-B3DE-F970-DFDE-87C9E7A869EE}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11757585" y="1084020"/>
+            <a:ext cx="656969" cy="173802"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="77" name="図 76">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA71189B-67DB-5F43-0D1E-7B92773095E4}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="13412755" y="1331556"/>
+            <a:ext cx="304800" cy="304800"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>431541</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>81642</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>684245</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>188555</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="78" name="グループ化 77">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EF0E2EE-1790-4FD2-817D-F37DCF9BFAF8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="10092612" y="5184321"/>
+          <a:ext cx="3703087" cy="835867"/>
+          <a:chOff x="10088724" y="1001097"/>
+          <a:chExt cx="3703087" cy="835867"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="79" name="正方形/長方形 78">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EE79E4A-4B4E-0060-B77C-B5E7D7028383}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10088724" y="1001097"/>
+            <a:ext cx="3703087" cy="835867"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="80" name="テキスト ボックス 79">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{595BCFCB-91BA-F551-C19E-4E67512CB8AA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10601805" y="1255027"/>
+            <a:ext cx="1670916" cy="413433"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+                <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>鉄道　駅</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="81" name="グラフィックス 80">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72AD4B73-045F-EE81-946C-F06FBE290288}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12">
+            <a:extLst>
+              <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+                <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId13"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10272675" y="1335239"/>
+            <a:ext cx="313088" cy="307154"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="82" name="直線コネクタ 81">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B38457CC-7455-6CE6-F32B-1863EA6F64DF}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10183107" y="1752774"/>
+            <a:ext cx="3539952" cy="18303"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:solidFill>
+              <a:srgbClr val="808080"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="83" name="四角形: 角を丸くする 82">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F9A5BC8-3831-A287-480F-8FC975E03775}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10282703" y="1082228"/>
+            <a:ext cx="659998" cy="173802"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="84" name="四角形: 角を丸くする 83">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4597B5D-DF55-0155-A6C1-D0577A163921}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11024918" y="1084234"/>
+            <a:ext cx="659996" cy="173802"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="85" name="四角形: 角を丸くする 84">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B0875F1-1B47-FAB8-0D42-5E0521DE73D8}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11757585" y="1084020"/>
+            <a:ext cx="656969" cy="173802"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="86" name="図 85">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CED53BE-CD0F-B4B8-3755-B9A9B1DB5040}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="13412755" y="1331556"/>
+            <a:ext cx="304800" cy="304800"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>175726</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>777</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>39655</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="87" name="グループ化 86">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{941A98B2-2AB0-4220-8979-236D8AC9914B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="10099221" y="6007359"/>
+          <a:ext cx="3703087" cy="835867"/>
+          <a:chOff x="10088724" y="1001097"/>
+          <a:chExt cx="3703087" cy="835867"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="88" name="正方形/長方形 87">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C9DA506-BFBD-58AA-B744-8A7B4CDEBCE2}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10088724" y="1001097"/>
+            <a:ext cx="3703087" cy="835867"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="89" name="テキスト ボックス 88">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33FA70B0-8A26-27F5-ED32-AB800FB29452}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10601805" y="1255027"/>
+            <a:ext cx="1670916" cy="413433"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+                <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>鉄道　駅</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="90" name="グラフィックス 89">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1CF56C7-6062-B20E-A0C5-1DB3A09CE06A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12">
+            <a:extLst>
+              <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+                <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId13"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10272675" y="1335239"/>
+            <a:ext cx="313088" cy="307154"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="91" name="直線コネクタ 90">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3A75206-6530-6EC5-7E29-23197698420E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10183107" y="1752774"/>
+            <a:ext cx="3539952" cy="18303"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:solidFill>
+              <a:srgbClr val="808080"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="92" name="四角形: 角を丸くする 91">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07ABD9E0-1512-D9B9-0A45-4CD565FF4EA2}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10282703" y="1082228"/>
+            <a:ext cx="659998" cy="173802"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="93" name="四角形: 角を丸くする 92">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E85C56FA-D654-E2F7-4351-7319CD0945C6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11024918" y="1084234"/>
+            <a:ext cx="659996" cy="173802"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="94" name="四角形: 角を丸くする 93">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E4B3AAE-9636-4DFA-EA65-93DCFE732261}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11757585" y="1084020"/>
+            <a:ext cx="656969" cy="173802"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="95" name="図 94">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EBCCB0D-638E-3DB9-B0D3-9D8947814AF7}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="13412755" y="1331556"/>
+            <a:ext cx="304800" cy="304800"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>574067</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>233506</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC7F16B5-9C9D-4C7F-8179-4BAE8A3A345F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="19776467" cy="11425381"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1609,8 +5235,52 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2790825" y="1743075"/>
-          <a:ext cx="3600450" cy="3600450"/>
+          <a:off x="1657350" y="3057525"/>
+          <a:ext cx="1943100" cy="1943100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>319574</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>108362</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8666C6C-80EF-6464-37F5-A543F6B299C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1419225" y="904875"/>
+          <a:ext cx="7815749" cy="1822862"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1900,6 +5570,22 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFFF9987-182B-49CB-9925-CFBF00C8FAEF}">
+  <dimension ref="E1"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="5:5">
+      <c r="E1" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E26E46FC-3C49-4A22-BEB4-D1E749DDFE28}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75"/>

--- a/01_設計/デザイン関係資料/spectra_chat_画面案.xlsx
+++ b/01_設計/デザイン関係資料/spectra_chat_画面案.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keita\Desktop\programing\nextjs\OpenDataChallenge\01_設計\デザイン関係資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5477603-3889-4B2D-BC02-2C691C2AE804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF53BFC6-F971-4E04-8EC1-481CB73D374D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="チャット操作画面" sheetId="1" r:id="rId1"/>
-    <sheet name="レイヤー操作画面" sheetId="3" r:id="rId2"/>
-    <sheet name="コンポーネント" sheetId="2" r:id="rId3"/>
+    <sheet name="チャット操作画面_0804" sheetId="4" r:id="rId1"/>
+    <sheet name="チャット操作画面_0803" sheetId="1" r:id="rId2"/>
+    <sheet name="レイヤー操作画面_0803" sheetId="3" r:id="rId3"/>
+    <sheet name="コンポーネント" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -82,11 +83,12 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF333333"/>
+      <color rgb="FF808080"/>
+      <color rgb="FFCCCCCC"/>
       <color rgb="FFCAB2FB"/>
+      <color rgb="FFC3FF4B"/>
       <color rgb="FFB28DD9"/>
-      <color rgb="FF808080"/>
-      <color rgb="FFC3FF4B"/>
-      <color rgb="FF333333"/>
     </mruColors>
   </colors>
   <extLst>
@@ -101,6 +103,1929 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>4572</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>115697</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58F62536-6A0D-4DA5-998E-472E7B20E360}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="19981559" cy="11307572"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>676274</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>53264</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>666749</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>135524</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="3" name="グループ化 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84F09728-F728-43A6-A7A4-AE656F8120B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="1360883" y="291389"/>
+          <a:ext cx="12313444" cy="6273510"/>
+          <a:chOff x="1360883" y="255445"/>
+          <a:chExt cx="12313444" cy="6273510"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="4" name="図 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54ED2D1A-4769-74AE-6539-B9FF44894A9B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="1360883" y="260821"/>
+            <a:ext cx="12313444" cy="6263804"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:extLst>
+            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a14:hiddenFill>
+            </a:ext>
+          </a:extLst>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="5" name="正方形/長方形 4">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95E76B4C-0DEA-A18B-0E4A-5774EFEC5E4E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1360884" y="255445"/>
+            <a:ext cx="692944" cy="6273510"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="C3FF4B"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="50800" dist="50800" sx="99000" sy="99000" algn="ctr" rotWithShape="0">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+              </a:schemeClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>668789</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>203027</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>13945</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>108770</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="テキスト ボックス 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBA2942E-D13D-48F7-AAFC-32B3D1D624BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="450408" y="1821583"/>
+          <a:ext cx="2525118" cy="716756"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" b="1">
+              <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>SPECTRA</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" b="1" baseline="0">
+              <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" b="1" baseline="0">
+              <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>CHAT</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" b="1">
+            <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>119458</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>188514</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>576658</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>169464</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="グラフィックス 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2CCCCA4-2104-49A6-B666-2CF3B784D794}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="1491058" y="426639"/>
+          <a:ext cx="457200" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>173991</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>107605</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>478791</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>174706</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="グラフィックス 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2302B9E7-CC10-4F21-AA19-E8735942688E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId5"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1545591" y="3917605"/>
+          <a:ext cx="304800" cy="305226"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>116227</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>199451</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>573427</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>200532</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="直線コネクタ 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC63B508-C17A-46DC-A5BD-35C884629B77}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1487827" y="3533201"/>
+          <a:ext cx="457200" cy="1081"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>185898</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>40184</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>490698</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>98805</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="グラフィックス 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3A64D7E-6DE5-4BD2-A8B2-CEC085EA626D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId7"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1557498" y="4564559"/>
+          <a:ext cx="304800" cy="296746"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>182702</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>137599</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>487502</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>204274</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="グラフィックス 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12F1CA6A-D685-42A2-BA99-223CC47389FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId9"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1554302" y="5852599"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>170457</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>222715</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>475257</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>49600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="グラフィックス 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4305F0C3-5539-48DE-A33F-E2E90832AE92}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId11"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1542057" y="5223340"/>
+          <a:ext cx="304800" cy="303135"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>459796</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>85702</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>26564</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="正方形/長方形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3ECBC82B-0BC5-424D-9F13-3A45B2939BFF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10044327" y="323827"/>
+          <a:ext cx="3674425" cy="6257948"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="50800" dir="10320000" algn="ctr" rotWithShape="0">
+            <a:schemeClr val="bg2">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>467296</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>227787</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>23632</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>125063</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="正方形/長方形 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77EDF185-F57D-43E0-B99A-DF6EA54F4309}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10068496" y="5704662"/>
+          <a:ext cx="3671136" cy="849776"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="25400" dir="14820000" algn="ctr" rotWithShape="0">
+            <a:schemeClr val="bg2">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="フローチャート: 代替処理 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67441DA6-DA2B-4F83-B161-73B639F28AB0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10134600" y="5842000"/>
+          <a:ext cx="2781300" cy="600075"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartAlternateProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="808080"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>672770</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>596570</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="楕円 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD19363E-DD91-4689-9AE8-FC8D0ED48E1D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13017170" y="5842000"/>
+          <a:ext cx="609600" cy="600075"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="C3FF4B"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>126352</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>9720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>507352</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>152595</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="グラフィックス 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B77C360-FD72-4B0D-B5BE-9D368D7A35F6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId13"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13156552" y="5962845"/>
+          <a:ext cx="381000" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>469873</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>13916</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>23594</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>224646</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="正方形/長方形 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8222E4F1-08AB-4D1B-9E8F-8257AC2D8D1B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10030816" y="499152"/>
+          <a:ext cx="3651269" cy="1181202"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="25400" dir="6420000" algn="ctr" rotWithShape="0">
+            <a:schemeClr val="bg2">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>530114</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>150900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>591908</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>124775</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="37" name="グループ化 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E296F97F-439D-0839-BEFC-AE5DE3033CA9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="10114645" y="865275"/>
+          <a:ext cx="3484841" cy="688250"/>
+          <a:chOff x="10101204" y="344240"/>
+          <a:chExt cx="3480040" cy="688223"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="31" name="四角形: 角を丸くする 30">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD26A8CE-DA47-4A56-8636-699A316EDC17}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10101370" y="344920"/>
+            <a:ext cx="1575095" cy="174788"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>吉祥寺から渋谷までの経路</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="32" name="四角形: 角を丸くする 31">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D77369E-2EBC-4AA4-8EED-EF9EE53D1487}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11740020" y="344240"/>
+            <a:ext cx="1841224" cy="174788"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>さいたま市の市街化調整区域を表示</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="33" name="四角形: 角を丸くする 32">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{062B1365-4C03-4A82-959F-3B3E20D826D1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10102246" y="597214"/>
+            <a:ext cx="1838749" cy="174788"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>浸水被害想定</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>5m</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>以上のエリア表示</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="34" name="四角形: 角を丸くする 33">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{918457D4-6567-40DE-9644-7CD658ACF5AD}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="12006927" y="596246"/>
+            <a:ext cx="1568562" cy="174788"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>新横浜駅からの</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>1km</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>の円表示</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="35" name="四角形: 角を丸くする 34">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6965E9A7-FC85-4220-A752-2137156A022A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10101204" y="853455"/>
+            <a:ext cx="1053017" cy="174788"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>東武東上線を表示</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="36" name="四角形: 角を丸くする 35">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1743C1B-6EF0-449F-AB54-73F5681993E0}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11221117" y="857675"/>
+            <a:ext cx="1946026" cy="174788"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CAB2FB"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800" b="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>現在利用可能なサイクルポートを取得</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>458278</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>62901</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>17971</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>34865</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="正方形/長方形 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50999DA1-8D16-B697-6B8F-627D26C76A78}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10019221" y="305519"/>
+          <a:ext cx="3657241" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="333333"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>512192</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>107830</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>305517</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>215660</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="テキスト ボックス 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7C9218C-46A4-BF16-089B-D8019261FB80}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10073135" y="350448"/>
+          <a:ext cx="1842099" cy="350448"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>チャットで質問</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>142083</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>198439</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>561183</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>122238</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="四角形: 角を丸くする 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BC402F6-0BC1-ED3A-4272-D5CD53122B8A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11780442" y="1865314"/>
+          <a:ext cx="1788319" cy="400049"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8163"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="CAB2FB"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>池袋駅を表示してください</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>628332</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>54372</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>368198</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>176114</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="59" name="グループ化 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{788A4120-D313-13E7-D496-B220DD3F844E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="10212863" y="2435622"/>
+          <a:ext cx="1793694" cy="836117"/>
+          <a:chOff x="10193015" y="2505076"/>
+          <a:chExt cx="1793696" cy="836117"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="41" name="四角形: 角を丸くする 40">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D26BD91A-8166-4218-BBB1-6D558C36AFDC}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10194132" y="2505076"/>
+            <a:ext cx="1787128" cy="761999"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 6622"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="CCCCCC"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="48" name="四角形: 上の 2 つの角を丸める 47">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9C88D86-4EA1-62B6-FE53-A9EBD818BC74}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="10800000">
+            <a:off x="10193015" y="3027589"/>
+            <a:ext cx="1793696" cy="255134"/>
+          </a:xfrm>
+          <a:prstGeom prst="round2SameRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="49" name="図 48">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39558383-2B3D-9639-88C2-C956295BF096}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10465299" y="2586015"/>
+            <a:ext cx="1259573" cy="359695"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="54" name="グラフィックス 53">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98D36AB2-97DD-F714-8EA5-E27B19104656}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15">
+            <a:extLst>
+              <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+                <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId16"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10264889" y="3078616"/>
+            <a:ext cx="186249" cy="190500"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="57" name="テキスト ボックス 56">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A695D394-6011-7F3E-F89D-4BFB43BBC241}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10408402" y="3018023"/>
+            <a:ext cx="786662" cy="323170"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:latin typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+                <a:ea typeface="Noto Sans JP" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              </a:rPr>
+              <a:t>表示切替</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1366,7 +3291,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2584,57 +4509,6 @@
       </xdr:cxnSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="31" name="四角形: 角を丸くする 30">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4257B93-1712-552F-E90D-17093CE8A7DD}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="10282703" y="1082228"/>
-            <a:ext cx="659998" cy="173802"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="CAB2FB"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
           <xdr:cNvPr id="32" name="四角形: 角を丸くする 31">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
@@ -5128,7 +7002,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -5248,15 +7122,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>319574</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>108362</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>100499</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>32162</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5279,7 +7153,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1419225" y="904875"/>
+          <a:off x="1885950" y="1066800"/>
           <a:ext cx="7815749" cy="1822862"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5554,6 +7428,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CFA8E1D-6CA4-49C4-BF09-3F870F4A7B3E}">
+  <dimension ref="E1"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="5:5">
+      <c r="E1" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="E1"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -5569,7 +7459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFFF9987-182B-49CB-9925-CFBF00C8FAEF}">
   <dimension ref="E1"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -5585,7 +7475,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E26E46FC-3C49-4A22-BEB4-D1E749DDFE28}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
